--- a/i18n/dk.xlsx
+++ b/i18n/dk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -5090,9 +5090,6 @@
     <t>3 fortløbende fugle: 3[point]; 4 fortløbende fugle: 5[point]; 5 fortløbende fugle: 8[point]</t>
   </si>
   <si>
-    <t>Disse bonuskort giver bonuspoint for en række af en vis længde i det tilhørende levested af fortløbende fugle med vingefang i stigende eller faldende størrelser. Rækken behøver ikke at bestå af alle fuglene i det pågældende levested, og den behøver heller ikke at starte eller slutte med den første eller sidste fugl i levestedet. En række må gerne inkludere to eller flere fugle med lige store vingefang. Som nævnt tidligere tæller vingefanget både på fugle ude flyveevne som en joker: I forhold til disse bonuskort kan du tildele en fugl uden flyveevne et valgfrit vingefang. Eksempel: Hvis vingefanget på de tre første fugle i dit vådområde er i stigende størrelser, men den fjerde fugl i dit vådområde har et mindre vingefang end den tredje fugl , er længden på din række tre, hvilket betyder, at bonuskortet Vådområdeanalytiker giver dig 3 point.</t>
-  </si>
-  <si>
     <t>Grassland Data Analyst</t>
   </si>
   <si>
@@ -5204,9 +5201,6 @@
   </si>
   <si>
     <t>Explanatory Text</t>
-  </si>
-  <si>
-    <t>Bird in Forest</t>
   </si>
   <si>
     <t>[bird] i [forest]</t>
@@ -5236,19 +5230,10 @@
     <t>Der er en målbrik af denne for hvert levested.</t>
   </si>
   <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
     <t>[bird] i [grassland]</t>
   </si>
   <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
     <t>[bird] i [wetland]</t>
-  </si>
-  <si>
-    <t>Egg in Forest</t>
   </si>
   <si>
     <t>[egg] i [forest]</t>
@@ -5281,19 +5266,10 @@
     </r>
   </si>
   <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
     <t>[egg] i [grassland]</t>
   </si>
   <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
     <t>[egg] i [wetland]</t>
-  </si>
-  <si>
-    <t>Cavity Nest Bird with Egg</t>
   </si>
   <si>
     <t>[cavity][bird] med [egg]</t>
@@ -5335,28 +5311,16 @@
     </r>
   </si>
   <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[bowl][bird] med [egg]</t>
   </si>
   <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[ground][bird] med [egg]</t>
   </si>
   <si>
     <t>Der er en målbrik af denne for hver redetype.</t>
   </si>
   <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[platform][bird] med [egg]</t>
-  </si>
-  <si>
-    <t>Egg in Cavity Nest</t>
   </si>
   <si>
     <t>[egg] i [cavity}</t>
@@ -5389,45 +5353,27 @@
     </r>
   </si>
   <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
     <t>[egg] i [bowl]</t>
   </si>
   <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
     <t>[egg] i [ground]</t>
   </si>
   <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
     <t>[egg] i [platform]</t>
   </si>
   <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
     <t>Sæt af [egg][egg][egg] i [wetland][grassland][forest]</t>
   </si>
   <si>
     <t>Et sæt af æg består af 1 æg i rækken vådområde, 1 æg i rækken med græs og 1 æg i rækken med skov. Tæl antallet af sæt.</t>
   </si>
   <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
     <t>Total [bird]</t>
   </si>
   <si>
     <t>Tæl det totale antal fuglekort, som spilleren har spillet.</t>
   </si>
   <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Forrådsmængde</t>
   </si>
   <si>
@@ -5443,81 +5389,54 @@
     <t>Antallet af fuglekort på hånden.</t>
   </si>
   <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
     <t>Fugle mere værd end 4 point</t>
   </si>
   <si>
     <t>Antallet af spillede fugle med en værdi over 4 point.</t>
   </si>
   <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
     <t>Fugle uden æg</t>
   </si>
   <si>
     <t>Antallet af dine spillede fugle, der ikke har nogen æg, når dette mål er nået.</t>
   </si>
   <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
     <t>Fugle i 1 række</t>
   </si>
   <si>
     <t>Antallet af dine spillede fugle på det levested, der er mest fuglerigt.</t>
   </si>
   <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
     <t>Fyldte kolonner</t>
   </si>
   <si>
     <t>Antallet af kolonner, hvor alle tre fuglepladser er fyldt ud.</t>
   </si>
   <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
     <t>Brunde effekter</t>
   </si>
   <si>
     <t>Antallet af dine spillede fugle, der har brune effekter efter, at de er aktiverede.</t>
   </si>
   <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
     <t>Hvide eller ingen effekter</t>
   </si>
   <si>
     <t>Antallet af dine spillede fugle, der enten ingen effekter har, eller har en ”når kortet spilles”-effekt.</t>
   </si>
   <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
     <t>Fugle med kort bagved</t>
   </si>
   <si>
     <t>Antallet af dine spillede fugle, der har mindst 1 kort gemt bag sig.</t>
   </si>
   <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
     <t>Fødeprisen for spillede fugle</t>
   </si>
   <si>
     <t>Regn fødeprisen på dine fugle sammen, husk kun at tælle 1 fødetype for fugle, der har en alternativ pris.</t>
   </si>
   <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>[invertebrate] i fødepriser på dine fugle</t>
   </si>
   <si>
@@ -5527,45 +5446,24 @@
     <t>Eksempel: For målet [fruit]+[seed] i fødepris på dine fugle, skal du kigge på fødeprisen i øverste venstre hjørne af alle dine spillede fugle og tælle alle [fruit] plus alle [seed]. Hvis en fugl har [fruit]/[seed] som fødepris (du betale [fruit] ELLER [seed] for at spille fuglen) tæller den kun som én føde for dette rundemål. Tæl ikke [wild] eller [nectar].</t>
   </si>
   <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>[fruit] + [seed] i fødepriser på dine fugle</t>
   </si>
   <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>[rodent] + [fish] i fødepriser på dine fugle</t>
   </si>
   <si>
-    <t>No Goal</t>
-  </si>
-  <si>
     <t>Intet mål</t>
   </si>
   <si>
     <t>I scorer inten mål i slutningen af denne runde. Behold jeres kuber. I hver af de efterfølgende runder har hver spiller 1 ekstra tur i forhold til normalt.</t>
   </si>
   <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
     <t>Næb peger mod venstre</t>
   </si>
   <si>
-    <t xml:space="preserve">Disse mål tæller kort, der viser en fugl, hvis næb peger i den pågældende retning. Fugle, hvis næb peger ligeud (eller lige op) tæller ikke med i nogen af disse mål. </t>
-  </si>
-  <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
     <t>Næb peger mod højre</t>
   </si>
   <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
     <t>Kuber på ”spil en fugl”</t>
   </si>
   <si>
@@ -5573,9 +5471,6 @@
   </si>
   <si>
     <t>Bemærk, at dette mål kræver, at du beholder dine handlingskuber i de rækker, hvor du har spillet dem.</t>
-  </si>
-  <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
   </si>
   <si>
     <r>
@@ -5597,42 +5492,6 @@
     </r>
   </si>
   <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
-    <t>In Forest</t>
-  </si>
-  <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
     <t>Translated</t>
   </si>
   <si>
@@ -5733,6 +5592,147 @@
   </si>
   <si>
     <t>Flavor text</t>
+  </si>
+  <si>
+    <t>Disse bonuskort giver bonuspoint for en række af en vis længde i det tilhørende levested af fortløbende fugle med vingefang i stigende eller faldende størrelser. Rækken behøver ikke at bestå af alle fuglene i det pågældende levested, og den behøver heller ikke at starte eller slutte med den første eller sidste fugl i levestedet. En række må gerne inkludere to eller flere fugle med lige store vingefang. Som nævnt tidligere tæller vingefanget både på fugle ude flyveevne som en joker: I forhold til disse bonuskort kan du tildele en fugl uden flyveevne et valgfrit vingefang. Eksempel: Hvis vingefanget på de tre første fugle i dit vådområde er i stigende størrelser, men den fjerde fugl i dit vådområde har et mindre vingefang end den tredje fugl, er længden på din række tre, hvilket betyder, at bonuskortet Vådområdeanalytiker giver dig 3 point.</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
+  </si>
+  <si>
+    <t>Disse mål tæller kort, der viser en fugl, hvis næb peger i den pågældende retning. Fugle, hvis næb peger ligeud (eller lige op) tæller ikke med i nogen af disse mål.</t>
   </si>
 </sst>
 </file>
@@ -5742,7 +5742,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;PRAWDA&quot;;&quot;PRAWDA&quot;;&quot;FAŁSZ&quot;"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5828,6 +5828,20 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5849,7 +5863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5883,6 +5897,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6116,7 +6132,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>1855</v>
+        <v>1808</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -6255,7 +6271,7 @@
         <v>36</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>1844</v>
+        <v>1797</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>22</v>
@@ -6500,7 +6516,7 @@
         <v>77</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>1845</v>
+        <v>1798</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="1" t="s">
@@ -6946,7 +6962,7 @@
         <v>149</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>1846</v>
+        <v>1799</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>22</v>
@@ -6957,7 +6973,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>1837</v>
+        <v>1790</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>150</v>
@@ -7051,7 +7067,7 @@
         <v>163</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>1844</v>
+        <v>1797</v>
       </c>
       <c r="I37" s="1"/>
       <c r="L37" s="1"/>
@@ -7313,7 +7329,7 @@
         <v>200</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>1847</v>
+        <v>1800</v>
       </c>
       <c r="G47" s="21"/>
       <c r="H47" s="1" t="s">
@@ -7707,7 +7723,7 @@
         <v>172</v>
       </c>
       <c r="H63" s="21" t="s">
-        <v>1853</v>
+        <v>1806</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>22</v>
@@ -7920,7 +7936,7 @@
         <v>289</v>
       </c>
       <c r="H71" s="21" t="s">
-        <v>1844</v>
+        <v>1797</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>22</v>
@@ -8415,7 +8431,7 @@
         <v>367</v>
       </c>
       <c r="H91" s="21" t="s">
-        <v>1844</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15" x14ac:dyDescent="0.25">
@@ -8772,7 +8788,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1838</v>
+        <v>1791</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>421</v>
@@ -9262,7 +9278,7 @@
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="21" t="s">
-        <v>1844</v>
+        <v>1797</v>
       </c>
       <c r="K125" s="1"/>
     </row>
@@ -9594,7 +9610,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1839</v>
+        <v>1792</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>548</v>
@@ -9957,7 +9973,7 @@
         <v>605</v>
       </c>
       <c r="F154" s="21" t="s">
-        <v>1848</v>
+        <v>1801</v>
       </c>
       <c r="G154" s="21"/>
       <c r="H154" s="1" t="s">
@@ -10551,7 +10567,7 @@
         <v>692</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1842</v>
+        <v>1795</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>13</v>
@@ -10615,7 +10631,7 @@
         <v>253</v>
       </c>
       <c r="H181" s="21" t="s">
-        <v>1849</v>
+        <v>1802</v>
       </c>
       <c r="J181" s="1"/>
     </row>
@@ -10857,7 +10873,7 @@
         <v>253</v>
       </c>
       <c r="H191" s="21" t="s">
-        <v>1849</v>
+        <v>1802</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>22</v>
@@ -11571,7 +11587,7 @@
         <v>824</v>
       </c>
       <c r="F218" s="21" t="s">
-        <v>1850</v>
+        <v>1803</v>
       </c>
       <c r="G218" s="21"/>
       <c r="H218" s="1" t="s">
@@ -11794,7 +11810,7 @@
         <v>253</v>
       </c>
       <c r="H227" s="21" t="s">
-        <v>1849</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="228" spans="1:12" ht="15" x14ac:dyDescent="0.25">
@@ -12420,7 +12436,7 @@
         <v>253</v>
       </c>
       <c r="H253" s="21" t="s">
-        <v>1849</v>
+        <v>1802</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>22</v>
@@ -12805,7 +12821,7 @@
         <v>991</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>1852</v>
+        <v>1805</v>
       </c>
       <c r="G268" s="4"/>
       <c r="J268" s="1" t="s">
@@ -13529,7 +13545,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="20" t="s">
-        <v>1841</v>
+        <v>1794</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>1115</v>
@@ -13845,7 +13861,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="19" t="s">
-        <v>1840</v>
+        <v>1793</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>1175</v>
@@ -13880,7 +13896,7 @@
         <v>1181</v>
       </c>
       <c r="H313" s="21" t="s">
-        <v>1854</v>
+        <v>1807</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>22</v>
@@ -14903,7 +14919,7 @@
         <v>1349</v>
       </c>
       <c r="F354" s="21" t="s">
-        <v>1851</v>
+        <v>1804</v>
       </c>
       <c r="G354" s="21"/>
       <c r="I354" s="1" t="s">
@@ -15607,7 +15623,7 @@
         <v>1447</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>1843</v>
+        <v>1796</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>1366</v>
@@ -17138,8 +17154,8 @@
       <c r="G35" s="9" t="s">
         <v>1684</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>1685</v>
+      <c r="H35" s="21" t="s">
+        <v>1809</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -17147,22 +17163,22 @@
         <v>1035</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>969</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>1687</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>1688</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>1684</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>1685</v>
+      <c r="H36" s="21" t="s">
+        <v>1809</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -17170,25 +17186,25 @@
         <v>1036</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>969</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>1690</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="9" t="s">
         <v>1691</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="G37" s="1" t="s">
         <v>1692</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="7" t="s">
         <v>1693</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -17196,25 +17212,25 @@
         <v>1037</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>969</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>1696</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>1697</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>1698</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>1699</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -17222,22 +17238,22 @@
         <v>1038</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>969</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>1702</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>1703</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>1684</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>1685</v>
+      <c r="H39" s="21" t="s">
+        <v>1809</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -17245,7 +17261,7 @@
         <v>1039</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>1366</v>
@@ -17256,7 +17272,7 @@
         <v>1040</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>1366</v>
@@ -17267,7 +17283,7 @@
         <v>1041</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>1366</v>
@@ -17278,7 +17294,7 @@
         <v>1042</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>1366</v>
@@ -17289,7 +17305,7 @@
         <v>1043</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>1366</v>
@@ -17300,7 +17316,7 @@
         <v>1044</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>1366</v>
@@ -17311,7 +17327,7 @@
         <v>1045</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>1366</v>
@@ -17322,7 +17338,7 @@
         <v>1046</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>1366</v>
@@ -17333,7 +17349,7 @@
         <v>1047</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>1366</v>
@@ -17344,7 +17360,7 @@
         <v>1048</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>1366</v>
@@ -17355,7 +17371,7 @@
         <v>1049</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>1366</v>
@@ -17366,7 +17382,7 @@
         <v>1050</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>1366</v>
@@ -17377,7 +17393,7 @@
         <v>1051</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>1366</v>
@@ -17423,104 +17439,104 @@
         <v>1545</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="23" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>1718</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="13" t="s">
         <v>1719</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>1720</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>1721</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>1722</v>
+      <c r="B3" s="23" t="s">
+        <v>1811</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>1724</v>
+      <c r="B4" s="23" t="s">
+        <v>1812</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1725</v>
+        <v>1721</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2013</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>1726</v>
+      <c r="B5" s="23" t="s">
+        <v>1813</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1727</v>
+        <v>1722</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2014</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>1729</v>
+      <c r="B6" s="23" t="s">
+        <v>1814</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1730</v>
+        <v>1724</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
       <c r="F6" s="12"/>
     </row>
@@ -17528,17 +17544,17 @@
       <c r="A7" s="1">
         <v>2017</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>1731</v>
+      <c r="B7" s="23" t="s">
+        <v>1815</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1732</v>
+        <v>1725</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
       <c r="F7" s="12"/>
     </row>
@@ -17546,17 +17562,17 @@
       <c r="A8" s="1">
         <v>2010</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>1733</v>
+      <c r="B8" s="23" t="s">
+        <v>1816</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1734</v>
+        <v>1726</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>1735</v>
+        <v>1727</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -17564,17 +17580,17 @@
       <c r="A9" s="1">
         <v>2008</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>1736</v>
+      <c r="B9" s="23" t="s">
+        <v>1817</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1737</v>
+        <v>1728</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1735</v>
+        <v>1727</v>
       </c>
       <c r="F9" s="12"/>
     </row>
@@ -17582,37 +17598,37 @@
       <c r="A10" s="1">
         <v>2021</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>1738</v>
+      <c r="B10" s="23" t="s">
+        <v>1818</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1739</v>
+        <v>1729</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>1735</v>
+        <v>1727</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>1740</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2022</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>1741</v>
+      <c r="B11" s="23" t="s">
+        <v>1819</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1742</v>
+        <v>1731</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>1735</v>
+        <v>1727</v>
       </c>
       <c r="F11" s="12"/>
     </row>
@@ -17620,17 +17636,17 @@
       <c r="A12" s="1">
         <v>2012</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>1743</v>
+      <c r="B12" s="23" t="s">
+        <v>1820</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1744</v>
+        <v>1732</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1745</v>
+        <v>1733</v>
       </c>
       <c r="F12" s="12"/>
     </row>
@@ -17638,17 +17654,17 @@
       <c r="A13" s="1">
         <v>2011</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>1746</v>
+      <c r="B13" s="23" t="s">
+        <v>1821</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1747</v>
+        <v>1734</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>1745</v>
+        <v>1733</v>
       </c>
       <c r="F13" s="12"/>
     </row>
@@ -17656,17 +17672,17 @@
       <c r="A14" s="1">
         <v>2015</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>1748</v>
+      <c r="B14" s="23" t="s">
+        <v>1822</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1749</v>
+        <v>1735</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1745</v>
+        <v>1733</v>
       </c>
       <c r="F14"/>
     </row>
@@ -17674,17 +17690,17 @@
       <c r="A15" s="1">
         <v>2016</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>1750</v>
+      <c r="B15" s="23" t="s">
+        <v>1823</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1751</v>
+        <v>1736</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>1745</v>
+        <v>1733</v>
       </c>
       <c r="F15" s="12"/>
     </row>
@@ -17692,17 +17708,17 @@
       <c r="A16" s="1">
         <v>2023</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>1752</v>
+      <c r="B16" s="23" t="s">
+        <v>1824</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>1753</v>
+        <v>1737</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1754</v>
+        <v>1738</v>
       </c>
       <c r="F16" s="12"/>
     </row>
@@ -17710,17 +17726,17 @@
       <c r="A17" s="1">
         <v>2024</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>1755</v>
+      <c r="B17" s="23" t="s">
+        <v>1825</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1756</v>
+        <v>1739</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1757</v>
+        <v>1740</v>
       </c>
       <c r="F17" s="12"/>
     </row>
@@ -17728,17 +17744,17 @@
       <c r="A18" s="1">
         <v>2020</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>1758</v>
+      <c r="B18" s="23" t="s">
+        <v>1826</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1759</v>
+        <v>1741</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1760</v>
+        <v>1742</v>
       </c>
       <c r="F18" s="12"/>
     </row>
@@ -17746,17 +17762,17 @@
       <c r="A19" s="1">
         <v>2003</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>1761</v>
+      <c r="B19" s="23" t="s">
+        <v>1743</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1762</v>
+        <v>1744</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1763</v>
+        <v>1745</v>
       </c>
       <c r="F19" s="12"/>
     </row>
@@ -17764,17 +17780,17 @@
       <c r="A20" s="1">
         <v>2004</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>1764</v>
+      <c r="B20" s="23" t="s">
+        <v>1827</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>1765</v>
+        <v>1746</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1766</v>
+        <v>1747</v>
       </c>
       <c r="F20" s="12"/>
     </row>
@@ -17782,17 +17798,17 @@
       <c r="A21" s="1">
         <v>2006</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>1767</v>
+      <c r="B21" s="23" t="s">
+        <v>1828</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1768</v>
+        <v>1748</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1769</v>
+        <v>1749</v>
       </c>
       <c r="F21" s="12"/>
     </row>
@@ -17800,17 +17816,17 @@
       <c r="A22" s="1">
         <v>2005</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>1770</v>
+      <c r="B22" s="23" t="s">
+        <v>1829</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1771</v>
+        <v>1750</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1772</v>
+        <v>1751</v>
       </c>
       <c r="F22" s="12"/>
     </row>
@@ -17818,17 +17834,17 @@
       <c r="A23" s="1">
         <v>2018</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>1773</v>
+      <c r="B23" s="23" t="s">
+        <v>1830</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1774</v>
+        <v>1752</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1775</v>
+        <v>1753</v>
       </c>
       <c r="F23" s="12"/>
     </row>
@@ -17836,17 +17852,17 @@
       <c r="A24" s="1">
         <v>2009</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>1776</v>
+      <c r="B24" s="23" t="s">
+        <v>1831</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1777</v>
+        <v>1754</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1778</v>
+        <v>1755</v>
       </c>
       <c r="F24" s="12"/>
     </row>
@@ -17854,17 +17870,17 @@
       <c r="A25" s="1">
         <v>2025</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>1779</v>
+      <c r="B25" s="23" t="s">
+        <v>1832</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1780</v>
+        <v>1756</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1781</v>
+        <v>1757</v>
       </c>
       <c r="F25" s="12"/>
     </row>
@@ -17872,17 +17888,17 @@
       <c r="A26" s="1">
         <v>2007</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>1782</v>
+      <c r="B26" s="23" t="s">
+        <v>1833</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1783</v>
+        <v>1758</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1784</v>
+        <v>1759</v>
       </c>
       <c r="F26" s="12"/>
     </row>
@@ -17890,17 +17906,17 @@
       <c r="A27" s="1">
         <v>2019</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>1785</v>
+      <c r="B27" s="23" t="s">
+        <v>1834</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1786</v>
+        <v>1760</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1787</v>
+        <v>1761</v>
       </c>
       <c r="F27" s="12"/>
     </row>
@@ -17908,94 +17924,94 @@
       <c r="A28" s="1">
         <v>2031</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>1788</v>
+      <c r="B28" s="23" t="s">
+        <v>1835</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>969</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1789</v>
+        <v>1762</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1790</v>
+        <v>1763</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>1791</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>2030</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>1792</v>
+      <c r="B29" s="23" t="s">
+        <v>1836</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>969</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1793</v>
+        <v>1765</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1790</v>
+        <v>1763</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>1791</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>2033</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>1794</v>
+      <c r="B30" s="23" t="s">
+        <v>1837</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>969</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1795</v>
+        <v>1766</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1790</v>
+        <v>1763</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>1791</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>2032</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>1796</v>
+      <c r="B31" s="23" t="s">
+        <v>1838</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>969</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1797</v>
+        <v>1767</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>1798</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>2026</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>1799</v>
+      <c r="B32" s="23" t="s">
+        <v>1839</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>969</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1800</v>
+        <v>1769</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1801</v>
+        <v>1855</v>
       </c>
       <c r="F32" s="12"/>
     </row>
@@ -18003,17 +18019,17 @@
       <c r="A33" s="1">
         <v>2027</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>1802</v>
+      <c r="B33" s="23" t="s">
+        <v>1840</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>969</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1803</v>
+        <v>1770</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1801</v>
+        <v>1855</v>
       </c>
       <c r="F33" s="12"/>
     </row>
@@ -18021,34 +18037,34 @@
       <c r="A34" s="1">
         <v>2029</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>1804</v>
+      <c r="B34" s="23" t="s">
+        <v>1841</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>969</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1805</v>
+        <v>1771</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1806</v>
+        <v>1772</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>1807</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>2028</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>1808</v>
+      <c r="B35" s="23" t="s">
+        <v>1842</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>969</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1809</v>
+        <v>1774</v>
       </c>
       <c r="E35"/>
       <c r="F35" s="12"/>
@@ -18057,8 +18073,8 @@
       <c r="A36" s="1">
         <v>2043</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>1810</v>
+      <c r="B36" s="24" t="s">
+        <v>1843</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>1366</v>
@@ -18071,8 +18087,8 @@
       <c r="A37" s="1">
         <v>2040</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>1811</v>
+      <c r="B37" s="23" t="s">
+        <v>1844</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>1366</v>
@@ -18085,8 +18101,8 @@
       <c r="A38" s="1">
         <v>2035</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>1812</v>
+      <c r="B38" s="23" t="s">
+        <v>1845</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>1366</v>
@@ -18099,8 +18115,8 @@
       <c r="A39" s="1">
         <v>2041</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>1813</v>
+      <c r="B39" s="23" t="s">
+        <v>1846</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>1366</v>
@@ -18113,8 +18129,8 @@
       <c r="A40" s="1">
         <v>2042</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>1814</v>
+      <c r="B40" s="23" t="s">
+        <v>1847</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>1366</v>
@@ -18127,8 +18143,8 @@
       <c r="A41" s="1">
         <v>2044</v>
       </c>
-      <c r="B41" s="12" t="s">
-        <v>1815</v>
+      <c r="B41" s="23" t="s">
+        <v>1848</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>1366</v>
@@ -18141,8 +18157,8 @@
       <c r="A42" s="1">
         <v>2036</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>1816</v>
+      <c r="B42" s="23" t="s">
+        <v>1849</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>1366</v>
@@ -18155,8 +18171,8 @@
       <c r="A43" s="1">
         <v>2034</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>1817</v>
+      <c r="B43" s="23" t="s">
+        <v>1850</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>1366</v>
@@ -18169,8 +18185,8 @@
       <c r="A44" s="1">
         <v>2037</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>1818</v>
+      <c r="B44" s="23" t="s">
+        <v>1851</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>1366</v>
@@ -18183,8 +18199,8 @@
       <c r="A45" s="1">
         <v>2038</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>1819</v>
+      <c r="B45" s="23" t="s">
+        <v>1852</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>1366</v>
@@ -18197,8 +18213,8 @@
       <c r="A46" s="1">
         <v>2039</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>1820</v>
+      <c r="B46" s="23" t="s">
+        <v>1853</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>1366</v>
@@ -18211,8 +18227,8 @@
       <c r="A47" s="1">
         <v>2045</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>1821</v>
+      <c r="B47" s="23" t="s">
+        <v>1854</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>1366</v>
@@ -18224,7 +18240,7 @@
   </sheetData>
   <autoFilter ref="A1:F47"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,normal"&amp;12&amp;KffffffStrona &amp;P</oddFooter>
@@ -18246,55 +18262,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1822</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1823</v>
+        <v>1776</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1824</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1825</v>
+        <v>1778</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1826</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1827</v>
+        <v>1780</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1828</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1829</v>
+        <v>1782</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1830</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1831</v>
+        <v>1784</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1832</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1833</v>
+        <v>1786</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1834</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.25">
@@ -18324,13 +18340,13 @@
         <v>1544</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>1835</v>
+        <v>1788</v>
       </c>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1836</v>
+        <v>1789</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="2"/>
